--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol_r2/post_rank_positive_return/staggered_10_accounts_hold_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol_r2/post_rank_positive_return/staggered_10_accounts_hold_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -466,12 +466,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.008990854637005219</v>
+        <v>-0.07074288367838255</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2643138473777447</v>
+        <v>0.1589707142420532</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.03692861933342879</v>
+        <v>-0.5355568394503156</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.05090425224305762</v>
+        <v>-0.685455026495902</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2473557350001961</v>
+        <v>0.1377709475300664</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.04105065005650134</v>
+        <v>-0.5775317840562089</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>12.39807949080034</v>
+        <v>9.465021263969206</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2115076816057028</v>
+        <v>-0.2104953617355578</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2250362567104131</v>
+        <v>0.2549778170836717</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.052618046443917</v>
+        <v>-0.8959525691951993</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.369983949217657</v>
+        <v>-1.20140622930488</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2582305833688003</v>
+        <v>0.2877493019117299</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8489018303517423</v>
+        <v>-0.7581896292728378</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>13.24583084489417</v>
+        <v>12.18913848735918</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.06186481752755779</v>
+        <v>0.1240498165231261</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2071720622644855</v>
+        <v>0.1895401763632059</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.289746961436461</v>
+        <v>0.6582904746227584</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.4150504433602413</v>
+        <v>0.9891716553723594</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.215784205151404</v>
+        <v>0.1582890850361438</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.2981552459361703</v>
+        <v>0.8180888783366289</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>13.19412606538749</v>
+        <v>13.17418174215395</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.1065183156392486</v>
+        <v>0.01111848119594416</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2042606878457488</v>
+        <v>0.2256689682478205</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.5448507691966632</v>
+        <v>0.09737694222076358</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.792775286918587</v>
+        <v>0.1380486643844007</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.155155609601747</v>
+        <v>0.1814040858414593</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.7164169531489232</v>
+        <v>0.06383854477961766</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>12.92356139613212</v>
+        <v>15.41999897692025</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3748941043315965</v>
+        <v>0.5106249773990335</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2457708019475539</v>
+        <v>0.2527586501153712</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.407138056050697</v>
+        <v>1.761688026194862</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.972911441125555</v>
+        <v>2.56117576957248</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1421662599410441</v>
+        <v>0.1392336695525326</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.75172497000314</v>
+        <v>3.834435331414911</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>15.85797552628778</v>
+        <v>14.42115457201823</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.04871110040986926</v>
+        <v>0.1059398280627217</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3375503827847132</v>
+        <v>0.350189503366147</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.379506213086384</v>
+        <v>0.6527677566959516</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5358997778565755</v>
+        <v>0.9487479268836781</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2239772684618125</v>
+        <v>0.1452313590565582</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.4020679240249478</v>
+        <v>1.379049286103751</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>13.09265737790623</v>
+        <v>12.61000207324046</v>
       </c>
     </row>
   </sheetData>
